--- a/data/trans_orig/IP07C16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>31981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49221</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>68316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90095</t>
+          <t>89421</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73754</t>
+          <t>72670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96552</t>
+          <t>95249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146840</t>
+          <t>146891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178786</t>
+          <t>176806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68623</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91153</t>
+          <t>90707</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85730</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>108180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161341</t>
+          <t>162834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192608</t>
+          <t>194103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>31540</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42019</t>
+          <t>41843</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>62812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28628</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>35544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52630</t>
+          <t>51193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44033</t>
+          <t>44098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107476</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133334</t>
+          <t>134817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112214</t>
+          <t>111628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138585</t>
+          <t>138578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227729</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>263319</t>
+          <t>265743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107019</t>
+          <t>107171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132199</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122374</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>148911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238069</t>
+          <t>236164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272780</t>
+          <t>277010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48446</t>
+          <t>48631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50515</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>66893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21307</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30723</t>
+          <t>30539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57527</t>
+          <t>57126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>42458</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10722</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78292</t>
+          <t>78622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>101596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96914</t>
+          <t>98949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121419</t>
+          <t>121926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183023</t>
+          <t>183692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69439</t>
+          <t>69307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>91965</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69846</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92916</t>
+          <t>91712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143207</t>
+          <t>144857</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176648</t>
+          <t>176188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>36767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66640</t>
+          <t>67094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24021</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>36413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18234</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30100</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62750</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>30351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39707</t>
+          <t>40226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57229</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131633</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>160430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145107</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>171065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>282303</t>
+          <t>284324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322660</t>
+          <t>324255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>109008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137522</t>
+          <t>137725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105097</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134851</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223408</t>
+          <t>222853</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>263010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46525</t>
+          <t>47279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32871</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>52875</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93579</t>
+          <t>92040</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32250</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33363</t>
+          <t>33192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21298</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86803</t>
+          <t>87846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113303</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>86607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114324</t>
+          <t>112701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181751</t>
+          <t>182757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217503</t>
+          <t>218721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>91719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116031</t>
+          <t>117084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81278</t>
+          <t>81202</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105759</t>
+          <t>106907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179722</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217320</t>
+          <t>216196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>26762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44732</t>
+          <t>45181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82490</t>
+          <t>82047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>26947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>41292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44358</t>
+          <t>44856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61306</t>
+          <t>60327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82028</t>
+          <t>81690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31936</t>
+          <t>32243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37276</t>
+          <t>35599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>44069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62679</t>
+          <t>64353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130054</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162465</t>
+          <t>162357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>135332</t>
+          <t>134576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166544</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>275300</t>
+          <t>274918</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318772</t>
+          <t>318754</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>121193</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152834</t>
+          <t>152691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124687</t>
+          <t>126125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155226</t>
+          <t>156471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>252808</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>300944</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40773</t>
+          <t>41040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>62383</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>37151</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>58875</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84450</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114198</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22903</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>795</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C16-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C16-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 89,29%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2007 (tasa de respuesta: 89,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19064</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13869</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24393</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>44,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19942</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25477</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14937</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25758</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19064</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13917</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24646</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20772</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15755</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26184</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21268</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15934</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26691</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15302</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26415</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>46,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20772</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15305</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>34124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49876</t>
+          <t>49628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2746</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4804</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9426</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9478</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6255</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42582</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42582</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>42582</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>42582</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>42582</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>42582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84617</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72363</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96599</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>77967</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>68316</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89421</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>67524</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>88104</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84617</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72670</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95249</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146891</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176806</t>
+          <t>178129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96911</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>108499</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80242</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70045</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90707</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70368</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91201</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>96911</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>85794</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>108180</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162834</t>
+          <t>161168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194103</t>
+          <t>192479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,58%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28023</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21186</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37553</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23927</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17061</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>31540</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>16863</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>31812</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,69%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28023</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21575</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37221</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>41917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62812</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5670</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2365</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10162</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5717</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10526</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17738</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4448</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3841</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4513</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1478</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>215954</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>215954</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>215954</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188598</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188598</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188598</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>215954</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>215954</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>215954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,67 +2091,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>21480</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27681</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>56,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>22394</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16804</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28449</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16487</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>28828</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>52,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>21480</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>16557</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27365</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>43,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51193</t>
+          <t>52073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -2204,67 +2204,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>17731</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12522</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23586</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>18504</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13473</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24533</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12506</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24127</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>34,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>17731</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>12745</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23565</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28510</t>
+          <t>29115</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -2312,74 +2312,74 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9830</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5840</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>10522</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6318</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>15627</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>19,4%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>28,81%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9830</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6001</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15635</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2093</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4118</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3666</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3650</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54246</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>125162</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>111979</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>138981</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>40,69%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>120303</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>106768</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>134817</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>106814</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>133056</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>41,65%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>125162</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>111628</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>138578</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>40,69%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227110</t>
+          <t>225786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>265743</t>
+          <t>264113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135413</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>120033</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>150038</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>39,03%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>48,78%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>120014</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>107171</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>134159</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>106118</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>133341</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>41,55%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,44%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135413</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>122234</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>148911</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>236164</t>
+          <t>236249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>277010</t>
+          <t>275181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,14%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>40598</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>31717</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>50859</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>39253</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>30084</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>48631</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>30838</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>13,59%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>40598</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>31900</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>51044</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66893</t>
+          <t>67449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94589</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5717</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10808</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>7763</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>4104</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>12905</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>13423</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5717</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2742</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10504</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3220,92 +3220,92 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3892</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1526</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4194</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5961</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>307576</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>429</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>288858</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>288858</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>288858</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>307576</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23694</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17693</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29386</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25026</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19271</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30539</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19231</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30948</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,77%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23694</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17845</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29135</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14382</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9412</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20079</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19609</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14369</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25639</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13956</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25340</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14382</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9799</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20977</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>26409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11999</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>13,87%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5122</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10711</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10005</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,04%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10915</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>13,87%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>18416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1260</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4651</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3805</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4441</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>823</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4313</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3895</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4065</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45162</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51017</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51017</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51017</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110456</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>99143</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>123266</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>89450</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>78622</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101596</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>78319</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101712</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110456</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>98949</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>121926</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183692</t>
+          <t>183763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216133</t>
+          <t>217595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68032</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>91952</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,33%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80141</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69307</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91965</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91291</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,12%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>80446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70134</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>91712</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144857</t>
+          <t>144445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176188</t>
+          <t>177726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27829</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20168</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36199</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27080</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>20323</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35728</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19521</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>35515</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,56%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27829</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20959</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>36767</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67094</t>
+          <t>66699</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2162</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5756</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5791</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2447</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7124</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>222481</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>222481</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>222481</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199748</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>222481</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>222481</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>222481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24100</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17944</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30223</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,82%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>30360</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23957</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36413</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24078</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36792</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24100</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18418</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30165</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62930</t>
+          <t>63898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23927</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17903</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>29970</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24090</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18115</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30351</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17866</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>30386</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,07%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,48%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23927</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>18029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29355</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57244</t>
+          <t>56860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4470</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>4240</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8735</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8081</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13295</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -5384,107 +5384,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5825</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5379</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4668</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5213</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>56152</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60126</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>158250</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>143652</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>172875</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,37%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>53,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>144835</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>160430</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>130708</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>159989</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>46,59%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>158250</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>140888</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>171065</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>48,87%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284324</t>
+          <t>283031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>324255</t>
+          <t>322840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>118755</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>105356</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134332</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,68%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,54%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>123839</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>109008</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>137725</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>111189</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>138806</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>118755</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>104619</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134653</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>222853</t>
+          <t>222562</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263010</t>
+          <t>261456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42216</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>32407</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>52911</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,34%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>36441</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>28458</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>47279</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>27163</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>45807</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>11,72%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>42216</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>33550</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>52875</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>65083</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92040</t>
+          <t>95838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4618</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>4859</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2156</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9753</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4493</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3270</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1228</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7511</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5594</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7109</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>323795</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>442</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>310890</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>310890</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>310890</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>323795</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el/la menor en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12525</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8335</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17404</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13093</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17725</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8467</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17603</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,91%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12525</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8628</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17226</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18157</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13424</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23407</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8292</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4862</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12986</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>13088</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18157</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13402</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33192</t>
+          <t>34334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5957</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10878</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,83%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9221</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13487</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13478</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,13%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5957</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2890</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10501</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>21510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30606</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100394</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>88164</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>113076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>100043</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>87846</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>112233</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>88309</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>113405</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100394</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>86607</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112701</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182757</t>
+          <t>182968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218721</t>
+          <t>218533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94322</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82046</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>107697</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103534</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91719</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>117084</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90017</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>115662</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>94322</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81202</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>106907</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>181017</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216196</t>
+          <t>217456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33814</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25713</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>44349</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>34676</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>26762</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>45181</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>26257</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>44975</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,25%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33814</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26590</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45083</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55805</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82047</t>
+          <t>82230</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7485</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13205</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3778</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8332</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8623</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7485</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13658</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7774,107 +7774,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1244</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3758</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4427</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1244</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4521</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>236016</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>236016</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>236016</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>243275</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>243275</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>243275</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>236016</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>236016</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>236016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37596</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30616</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44756</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>33684</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26947</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>41292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26170</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40189</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>47,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>37596</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>30465</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44856</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60327</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>82024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21451</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35623</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>47,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>25445</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18489</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>32243</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19673</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32605</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>28212</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>21482</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35599</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64353</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13503</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6836</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3393</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12375</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11693</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8406</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4739</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13848</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10082</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -8343,72 +8343,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3383</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3508</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7537</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7784</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1615</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4928</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5979</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74885</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74885</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74885</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>71090</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74885</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74885</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74885</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>150515</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>132750</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>164721</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>146820</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>132149</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>162357</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>130353</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>161850</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>42,56%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>150515</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>134576</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>165548</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>43,31%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>274918</t>
+          <t>275639</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318754</t>
+          <t>321273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>140691</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>125511</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>156846</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,48%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>36,11%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,13%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137271</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>122242</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>152691</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>122752</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>152332</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,79%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>140691</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>126125</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>156471</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>40,48%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252808</t>
+          <t>257325</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>298504</t>
+          <t>300100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>48177</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>38379</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>59931</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>17,24%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>50733</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>41040</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>62274</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>62960</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>48177</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>58875</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84793</t>
+          <t>82967</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116119</t>
+          <t>114404</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8156</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4095</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13903</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>7286</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3678</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>13233</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>12627</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>8156</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4389</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>14831</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2859</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6722</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>347539</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>344970</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>344970</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>344970</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>347539</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
